--- a/data/trans_orig/IP18_E_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18_E_R-Estudios-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>68617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137957</t>
+          <t>137865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142293</t>
+          <t>142289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>341149</t>
+          <t>341418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354318</t>
+          <t>354555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>376036</t>
+          <t>375891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>390831</t>
+          <t>390378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>723881</t>
+          <t>722880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>741707</t>
+          <t>741670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138169</t>
+          <t>138844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106832</t>
+          <t>105750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120676</t>
+          <t>120251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236931</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255133</t>
+          <t>256242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52867</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559159</t>
+          <t>559176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>579433</t>
+          <t>579435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1106733</t>
+          <t>1106676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1133410</t>
+          <t>1134445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>53423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68170</t>
+          <t>67135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94847</t>
+          <t>94904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83738</t>
+          <t>83720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75430</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160663</t>
+          <t>161362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398255</t>
+          <t>398009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411937</t>
+          <t>412384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>441018</t>
+          <t>441025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>455325</t>
+          <t>455621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>845806</t>
+          <t>845040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>865471</t>
+          <t>864500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26812</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>27164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130942</t>
+          <t>130354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144127</t>
+          <t>143401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138873</t>
+          <t>138074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152654</t>
+          <t>151693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274521</t>
+          <t>275132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292750</t>
+          <t>292708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26163</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45581</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>662403</t>
+          <t>662898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>682176</t>
+          <t>682766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1289666</t>
+          <t>1290116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1317211</t>
+          <t>1317305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>48261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59962</t>
+          <t>59868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87507</t>
+          <t>87057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111449</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117180</t>
+          <t>117168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>411177</t>
+          <t>411911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424517</t>
+          <t>425098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,82 +4297,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>421787</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>414810</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>427111</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>841045</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>830428</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>848586</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>421787</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>414206</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>427011</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>841045</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>830936</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>848922</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,82 +4410,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9299</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21600</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>32241</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>24700</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>42858</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14623</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9399</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22204</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>32241</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>24364</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>42350</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127863</t>
+          <t>126999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141384</t>
+          <t>140825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138134</t>
+          <t>137748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153258</t>
+          <t>153369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271414</t>
+          <t>270989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291000</t>
+          <t>290745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32018</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>34034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>53790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85082</t>
+          <t>84943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90261</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133398</t>
+          <t>135719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150024</t>
+          <t>150255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51778</t>
+          <t>51561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
